--- a/out/C01_chronic_care_patient_journey/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/C01_chronic_care_patient_journey/agent3/agent3_test_cases_with_paths.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>5 test(s): TC-FT126, TC-FT127, TC-FT128, TC-FT129, TC-FT130</t>
+          <t>5 test(s): TC-FT125, TC-FT126, TC-FT127, TC-FT128, TC-FT129</t>
         </is>
       </c>
       <c r="Q9" s="8" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>5 test(s): TC-FT133, TC-FT134, TC-FT135, TC-FT136, TC-FT137</t>
+          <t>5 test(s): TC-FT132, TC-FT133, TC-FT134, TC-FT135, TC-FT136</t>
         </is>
       </c>
       <c r="Q10" s="8" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>70 test(s): TC-FT09, TC-FT10, TC-FT11, TC-FT12, TC-FT103, TC-FT13 ...</t>
+          <t>69 test(s): TC-FT09, TC-FT10, TC-FT11, TC-FT12, TC-FT103, TC-FT13 ...</t>
         </is>
       </c>
       <c r="Q15" s="8" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE164"/>
+  <dimension ref="A1:AE163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
@@ -22021,22 +22021,22 @@
       </c>
       <c r="H132" s="6" t="inlineStr">
         <is>
-          <t>Q21 quotes the answer given at Q19</t>
+          <t>Q21 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>Prove Q21's wording is built from the answer given at Q19, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q21 refuses an answer that breaks its stated rule. The rule is: at least 5 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr">
@@ -22052,7 +22052,7 @@
       <c r="N132" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor
-then: At Q21, type “xxxxx”, then submit.</t>
+then: At Q21, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O132" s="6" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="Q132" s="6" t="inlineStr">
         <is>
-          <t>At Q21, type “xxxxx”, then submit.</t>
+          <t>At Q21, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R132" s="6" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="W132" s="6" t="inlineStr">
         <is>
-          <t>1. Q21's wording includes: Concept A</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X132" s="6" t="inlineStr">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="AD132" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE132" s="6" t="inlineStr">
@@ -22208,7 +22208,7 @@
       <c r="N133" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor
-then: At Q21, type a 500-character answer, then submit.</t>
+then: At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O133" s="6" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="Q133" s="6" t="inlineStr">
         <is>
-          <t>At Q21, type a 500-character answer, then submit.</t>
+          <t>At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R133" s="6" t="inlineStr">
@@ -22333,22 +22333,22 @@
       </c>
       <c r="H134" s="6" t="inlineStr">
         <is>
-          <t>Q21 rejects an invalid answer</t>
+          <t>Q21 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>Prove Q21 refuses an answer that breaks its stated rule. The rule is: at least 5 characters; at most 500 characters</t>
+          <t>Prove Q21 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr">
@@ -22364,7 +22364,7 @@
       <c r="N134" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor
-then: At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+then: At Q21, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O134" s="6" t="inlineStr">
@@ -22379,17 +22379,17 @@
       </c>
       <c r="Q134" s="6" t="inlineStr">
         <is>
-          <t>At Q21, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q21, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R134" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21  (refused at Q21; respondent stays put)</t>
         </is>
       </c>
       <c r="S134" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21</t>
         </is>
       </c>
       <c r="T134" s="6" t="inlineStr">
@@ -22399,22 +22399,23 @@
       </c>
       <c r="U134" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17</t>
+          <t>Q14, Q17, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="V134" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W134" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q21</t>
         </is>
       </c>
       <c r="X134" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y134" s="6" t="inlineStr">
@@ -22444,12 +22445,12 @@
       </c>
       <c r="AD134" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE134" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -22459,7 +22460,7 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>DT3</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
@@ -22474,7 +22475,7 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
@@ -22489,27 +22490,27 @@
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>Q21 allows a blank answer, being optional</t>
+          <t>DT3 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>Prove Q21 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove that answering DT3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q21.</t>
+          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as DT3.</t>
         </is>
       </c>
       <c r="M135" s="6" t="inlineStr">
@@ -22519,8 +22520,8 @@
       </c>
       <c r="N135" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor
-then: At Q21, type 3 spaces and nothing else, then submit.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O135" s="6" t="inlineStr">
@@ -22530,22 +22531,22 @@
       </c>
       <c r="P135" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q21 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q21 is the one the claim turns on.</t>
+          <t>Every answer before DT3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT3 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q135" s="6" t="inlineStr">
         <is>
-          <t>At Q21, type 3 spaces and nothing else, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R135" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21  (refused at Q21; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
       <c r="S135" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="T135" s="6" t="inlineStr">
@@ -22555,23 +22556,22 @@
       </c>
       <c r="U135" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17, DT3, D1, D2, D3, D4, Q22, Q23</t>
+          <t>Q14, Q17</t>
         </is>
       </c>
       <c r="V135" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W135" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q21</t>
+          <t>1. the next question shown is D1</t>
         </is>
       </c>
       <c r="X135" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y135" s="6" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="Z135" s="6" t="inlineStr">
         <is>
-          <t>Q21 | What most influenced your choice? | text | — | Validate: {"min_length": 5, "max_length": 500}</t>
+          <t>DT3 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
         </is>
       </c>
       <c r="AA135" s="6" t="inlineStr">
@@ -22601,12 +22601,12 @@
       </c>
       <c r="AD135" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE135" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
+          <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
       </c>
     </row>
@@ -22616,7 +22616,7 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>DT3</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -22646,12 +22646,12 @@
       </c>
       <c r="H136" s="6" t="inlineStr">
         <is>
-          <t>DT3 accepts a normal answer and the survey moves on</t>
+          <t>D1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering DT3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="L136" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as DT3.</t>
+          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D1.</t>
         </is>
       </c>
       <c r="M136" s="6" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="P136" s="6" t="inlineStr">
         <is>
-          <t>Every answer before DT3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT3 is the one the claim turns on.</t>
+          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q136" s="6" t="inlineStr">
@@ -22722,7 +22722,8 @@
       </c>
       <c r="W136" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is D1</t>
+          <t>1. D1 is on screen
+2. the next question shown is D2</t>
         </is>
       </c>
       <c r="X136" s="6" t="inlineStr">
@@ -22737,7 +22738,7 @@
       </c>
       <c r="Z136" s="6" t="inlineStr">
         <is>
-          <t>DT3 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
+          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
       <c r="AA136" s="6" t="inlineStr">
@@ -22787,12 +22788,12 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -22802,22 +22803,22 @@
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>D1 accepts a normal answer and the survey moves on</t>
+          <t>D1 blocks a blank answer</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr">
@@ -22832,13 +22833,13 @@
       </c>
       <c r="N137" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx
+then: At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O137" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P137" s="6" t="inlineStr">
@@ -22848,17 +22849,17 @@
       </c>
       <c r="Q137" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R137" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1  (refused at D1; respondent stays put)</t>
         </is>
       </c>
       <c r="S137" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1</t>
         </is>
       </c>
       <c r="T137" s="6" t="inlineStr">
@@ -22868,23 +22869,23 @@
       </c>
       <c r="U137" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17</t>
+          <t>Q14, Q17, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="V137" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W137" s="6" t="inlineStr">
         <is>
-          <t>1. D1 is on screen
-2. the next question shown is D2</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D1</t>
         </is>
       </c>
       <c r="X137" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y137" s="6" t="inlineStr">
@@ -22914,7 +22915,7 @@
       </c>
       <c r="AD137" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE137" s="6" t="inlineStr">
@@ -22944,42 +22945,42 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
         <is>
-          <t>D1 blocks a blank answer</t>
+          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D1.</t>
+          <t>Travel path P05 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
         </is>
       </c>
       <c r="M138" s="6" t="inlineStr">
@@ -22990,12 +22991,12 @@
       <c r="N138" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx
-then: At D1, select nothing at all, then submit.</t>
+then: At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="O138" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P138" s="6" t="inlineStr">
@@ -23005,43 +23006,42 @@
       </c>
       <c r="Q138" s="6" t="inlineStr">
         <is>
-          <t>At D1, select nothing at all, then submit.</t>
+          <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
       <c r="R138" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1  (refused at D1; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
       <c r="S138" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="T138" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U138" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17, D2, D3, D4, Q22, Q23</t>
+          <t>Q14, Q17</t>
         </is>
       </c>
       <c r="V138" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W138" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D1</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X138" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y138" s="6" t="inlineStr">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="AD138" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE138" s="6" t="inlineStr">
@@ -23116,12 +23116,12 @@
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O1 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'North' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
@@ -23147,7 +23147,7 @@
       <c r="N139" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx
-then: At D1, choose “North”, then submit.</t>
+then: At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="O139" s="6" t="inlineStr">
@@ -23162,7 +23162,7 @@
       </c>
       <c r="Q139" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “North”, then submit.</t>
+          <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
       <c r="R139" s="6" t="inlineStr">
@@ -23272,12 +23272,12 @@
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O2 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'South' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
@@ -23303,7 +23303,7 @@
       <c r="N140" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx
-then: At D1, choose “South”, then submit.</t>
+then: At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="O140" s="6" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="Q140" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “South”, then submit.</t>
+          <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
       <c r="R140" s="6" t="inlineStr">
@@ -23428,12 +23428,12 @@
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O3 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'East' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
@@ -23459,7 +23459,7 @@
       <c r="N141" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx
-then: At D1, choose “East”, then submit.</t>
+then: At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="O141" s="6" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="Q141" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “East”, then submit.</t>
+          <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
       <c r="R141" s="6" t="inlineStr">
@@ -23584,12 +23584,12 @@
       </c>
       <c r="H142" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O4 is open</t>
+          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
         </is>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'West' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
@@ -23615,7 +23615,7 @@
       <c r="N142" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx
-then: At D1, choose “West”, then submit.</t>
+then: At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="O142" s="6" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="Q142" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “West”, then submit.</t>
+          <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
       <c r="R142" s="6" t="inlineStr">
@@ -23710,7 +23710,7 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -23725,42 +23725,42 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_REGION admits a respondent while D1-O5 is open</t>
+          <t>D2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_REGION lets a 'Central' respondent through while that group is below its target.</t>
+          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr">
         <is>
-          <t>Travel path P05 (QUOTA_REGION cell already full (North) — measured on D1) as far as D1.</t>
+          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D2.</t>
         </is>
       </c>
       <c r="M143" s="6" t="inlineStr">
@@ -23770,8 +23770,8 @@
       </c>
       <c r="N143" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx
-then: At D1, choose “Central”, then submit.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O143" s="6" t="inlineStr">
@@ -23781,12 +23781,12 @@
       </c>
       <c r="P143" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D1 is the one the claim turns on.</t>
+          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q143" s="6" t="inlineStr">
         <is>
-          <t>At D1, choose “Central”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R143" s="6" t="inlineStr">
@@ -23801,7 +23801,7 @@
       </c>
       <c r="T143" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q2, Q3</t>
         </is>
       </c>
       <c r="U143" s="6" t="inlineStr">
@@ -23816,7 +23816,8 @@
       </c>
       <c r="W143" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. D2 is on screen
+2. the next question shown is D3</t>
         </is>
       </c>
       <c r="X143" s="6" t="inlineStr">
@@ -23831,7 +23832,7 @@
       </c>
       <c r="Z143" s="6" t="inlineStr">
         <is>
-          <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
+          <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
         </is>
       </c>
       <c r="AA143" s="6" t="inlineStr">
@@ -23851,7 +23852,7 @@
       </c>
       <c r="AD143" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE143" s="6" t="inlineStr">
@@ -23881,12 +23882,12 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -23896,22 +23897,22 @@
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>D2 accepts a normal answer and the survey moves on</t>
+          <t>D2 blocks a blank answer</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr">
@@ -23926,13 +23927,13 @@
       </c>
       <c r="N144" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North
+then: At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O144" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P144" s="6" t="inlineStr">
@@ -23942,17 +23943,17 @@
       </c>
       <c r="Q144" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R144" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
         </is>
       </c>
       <c r="S144" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2</t>
         </is>
       </c>
       <c r="T144" s="6" t="inlineStr">
@@ -23962,23 +23963,23 @@
       </c>
       <c r="U144" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17</t>
+          <t>Q14, Q17, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="V144" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W144" s="6" t="inlineStr">
         <is>
-          <t>1. D2 is on screen
-2. the next question shown is D3</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D2</t>
         </is>
       </c>
       <c r="X144" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y144" s="6" t="inlineStr">
@@ -24008,7 +24009,7 @@
       </c>
       <c r="AD144" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE144" s="6" t="inlineStr">
@@ -24038,42 +24039,42 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>5. Quota / Stateful</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>D2 blocks a blank answer</t>
+          <t>QUOTA_AGE admits a respondent while D2-O1 is open</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove QUOTA_AGE lets a '21-29' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
         </is>
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D2.</t>
+          <t>Travel path P06 (QUOTA_AGE cell already full (21-29) — measured on D2) as far as D2.</t>
         </is>
       </c>
       <c r="M145" s="6" t="inlineStr">
@@ -24084,12 +24085,12 @@
       <c r="N145" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North
-then: At D2, select nothing at all, then submit.</t>
+then: At D2, choose “21-29”, then submit.</t>
         </is>
       </c>
       <c r="O145" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P145" s="6" t="inlineStr">
@@ -24099,43 +24100,42 @@
       </c>
       <c r="Q145" s="6" t="inlineStr">
         <is>
-          <t>At D2, select nothing at all, then submit.</t>
+          <t>At D2, choose “21-29”, then submit.</t>
         </is>
       </c>
       <c r="R145" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2  (refused at D2; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
       <c r="S145" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="T145" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U145" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17, D3, D4, Q22, Q23</t>
+          <t>Q14, Q17</t>
         </is>
       </c>
       <c r="V145" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W145" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D2</t>
+          <t>1. the respondent is allowed to continue</t>
         </is>
       </c>
       <c r="X145" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y145" s="6" t="inlineStr">
@@ -24165,7 +24165,7 @@
       </c>
       <c r="AD145" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
         </is>
       </c>
       <c r="AE145" s="6" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_AGE admits a respondent while D2-O1 is open</t>
+          <t>QUOTA_AGE admits a respondent while D2-O2 is open</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_AGE lets a '21-29' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_AGE lets a '30-39' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J146" s="6" t="inlineStr">
@@ -24241,7 +24241,7 @@
       <c r="N146" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North
-then: At D2, choose “21-29”, then submit.</t>
+then: At D2, choose “30-39”, then submit.</t>
         </is>
       </c>
       <c r="O146" s="6" t="inlineStr">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="Q146" s="6" t="inlineStr">
         <is>
-          <t>At D2, choose “21-29”, then submit.</t>
+          <t>At D2, choose “30-39”, then submit.</t>
         </is>
       </c>
       <c r="R146" s="6" t="inlineStr">
@@ -24366,12 +24366,12 @@
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_AGE admits a respondent while D2-O2 is open</t>
+          <t>QUOTA_AGE admits a respondent while D2-O3 is open</t>
         </is>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_AGE lets a '30-39' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_AGE lets a '40-49' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
@@ -24397,7 +24397,7 @@
       <c r="N147" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North
-then: At D2, choose “30-39”, then submit.</t>
+then: At D2, choose “40-49”, then submit.</t>
         </is>
       </c>
       <c r="O147" s="6" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="Q147" s="6" t="inlineStr">
         <is>
-          <t>At D2, choose “30-39”, then submit.</t>
+          <t>At D2, choose “40-49”, then submit.</t>
         </is>
       </c>
       <c r="R147" s="6" t="inlineStr">
@@ -24522,12 +24522,12 @@
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_AGE admits a respondent while D2-O3 is open</t>
+          <t>QUOTA_AGE admits a respondent while D2-O4 is open</t>
         </is>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_AGE lets a '40-49' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_AGE lets a '50-59' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J148" s="6" t="inlineStr">
@@ -24553,7 +24553,7 @@
       <c r="N148" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North
-then: At D2, choose “40-49”, then submit.</t>
+then: At D2, choose “50-59”, then submit.</t>
         </is>
       </c>
       <c r="O148" s="6" t="inlineStr">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="Q148" s="6" t="inlineStr">
         <is>
-          <t>At D2, choose “40-49”, then submit.</t>
+          <t>At D2, choose “50-59”, then submit.</t>
         </is>
       </c>
       <c r="R148" s="6" t="inlineStr">
@@ -24678,12 +24678,12 @@
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_AGE admits a respondent while D2-O4 is open</t>
+          <t>QUOTA_AGE admits a respondent while D2-O5 is open</t>
         </is>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_AGE lets a '50-59' respondent through while that group is below its target.</t>
+          <t>Prove QUOTA_AGE lets a '60+' respondent through while that group is below its target.</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
@@ -24709,7 +24709,7 @@
       <c r="N149" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North
-then: At D2, choose “50-59”, then submit.</t>
+then: At D2, choose “60+”, then submit.</t>
         </is>
       </c>
       <c r="O149" s="6" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="Q149" s="6" t="inlineStr">
         <is>
-          <t>At D2, choose “50-59”, then submit.</t>
+          <t>At D2, choose “60+”, then submit.</t>
         </is>
       </c>
       <c r="R149" s="6" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
@@ -24819,42 +24819,42 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>5. Quota / Stateful</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>6. Termination / Disposition</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
-          <t>QUOTA_AGE admits a respondent while D2-O5 is open</t>
+          <t>D3 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>Prove QUOTA_AGE lets a '60+' respondent through while that group is below its target.</t>
+          <t>Prove that answering D3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>Quotas decide who gets turned away. Getting this wrong unbalances the whole sample.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr">
         <is>
-          <t>Travel path P06 (QUOTA_AGE cell already full (21-29) — measured on D2) as far as D2.</t>
+          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D3.</t>
         </is>
       </c>
       <c r="M150" s="6" t="inlineStr">
@@ -24864,8 +24864,8 @@
       </c>
       <c r="N150" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North
-then: At D2, choose “60+”, then submit.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O150" s="6" t="inlineStr">
@@ -24875,12 +24875,12 @@
       </c>
       <c r="P150" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D2 is the one the claim turns on.</t>
+          <t>Every answer before D3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D3 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q150" s="6" t="inlineStr">
         <is>
-          <t>At D2, choose “60+”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R150" s="6" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="T150" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q2, Q3</t>
         </is>
       </c>
       <c r="U150" s="6" t="inlineStr">
@@ -24910,7 +24910,8 @@
       </c>
       <c r="W150" s="6" t="inlineStr">
         <is>
-          <t>1. the respondent is allowed to continue</t>
+          <t>1. D3 is on screen
+2. the next question shown is D4</t>
         </is>
       </c>
       <c r="X150" s="6" t="inlineStr">
@@ -24925,7 +24926,7 @@
       </c>
       <c r="Z150" s="6" t="inlineStr">
         <is>
-          <t>D2 | Which age group describes you? | single | 21-29; 30-39; 40-49; 50-59; 60+ | Always show</t>
+          <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
         </is>
       </c>
       <c r="AA150" s="6" t="inlineStr">
@@ -24945,7 +24946,7 @@
       </c>
       <c r="AD150" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the counting is accurate, only that the boundary behaves as stated at the moment tested.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE150" s="6" t="inlineStr">
@@ -24975,12 +24976,12 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -24990,22 +24991,22 @@
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>D3 accepts a normal answer and the survey moves on</t>
+          <t>D3 blocks a blank answer</t>
         </is>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove D3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr">
@@ -25020,13 +25021,13 @@
       </c>
       <c r="N151" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29
+then: At D3, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O151" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P151" s="6" t="inlineStr">
@@ -25036,17 +25037,17 @@
       </c>
       <c r="Q151" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D3, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R151" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3  (refused at D3; respondent stays put)</t>
         </is>
       </c>
       <c r="S151" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3</t>
         </is>
       </c>
       <c r="T151" s="6" t="inlineStr">
@@ -25056,23 +25057,23 @@
       </c>
       <c r="U151" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17</t>
+          <t>Q14, Q17, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="V151" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W151" s="6" t="inlineStr">
         <is>
-          <t>1. D3 is on screen
-2. the next question shown is D4</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D3</t>
         </is>
       </c>
       <c r="X151" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y151" s="6" t="inlineStr">
@@ -25102,7 +25103,7 @@
       </c>
       <c r="AD151" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE151" s="6" t="inlineStr">
@@ -25117,7 +25118,7 @@
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
@@ -25132,12 +25133,12 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
@@ -25147,27 +25148,27 @@
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>D3 blocks a blank answer</t>
+          <t>D4 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>Prove D3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering D4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D3.</t>
+          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D4.</t>
         </is>
       </c>
       <c r="M152" s="6" t="inlineStr">
@@ -25177,33 +25178,33 @@
       </c>
       <c r="N152" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29
-then: At D3, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O152" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P152" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D3 is the one the claim turns on.</t>
+          <t>Every answer before D4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D4 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q152" s="6" t="inlineStr">
         <is>
-          <t>At D3, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R152" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3  (refused at D3; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
       <c r="S152" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="T152" s="6" t="inlineStr">
@@ -25213,23 +25214,23 @@
       </c>
       <c r="U152" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17, D4, Q22, Q23</t>
+          <t>Q14, Q17</t>
         </is>
       </c>
       <c r="V152" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W152" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D3</t>
+          <t>1. D4 is on screen
+2. the next question shown is Q22</t>
         </is>
       </c>
       <c r="X152" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y152" s="6" t="inlineStr">
@@ -25239,7 +25240,7 @@
       </c>
       <c r="Z152" s="6" t="inlineStr">
         <is>
-          <t>D3 | How do you describe your gender? | single | Woman; Man; Non-binary; Prefer to self-describe; Prefer not to say | Always show</t>
+          <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
         </is>
       </c>
       <c r="AA152" s="6" t="inlineStr">
@@ -25259,7 +25260,7 @@
       </c>
       <c r="AD152" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE152" s="6" t="inlineStr">
@@ -25289,12 +25290,12 @@
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
@@ -25304,22 +25305,22 @@
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>D4 accepts a normal answer and the survey moves on</t>
+          <t>D4 blocks a blank answer</t>
         </is>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering D4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove D4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr">
@@ -25334,13 +25335,13 @@
       </c>
       <c r="N153" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman
+then: At D4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O153" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P153" s="6" t="inlineStr">
@@ -25350,17 +25351,17 @@
       </c>
       <c r="Q153" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At D4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R153" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4  (refused at D4; respondent stays put)</t>
         </is>
       </c>
       <c r="S153" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4</t>
         </is>
       </c>
       <c r="T153" s="6" t="inlineStr">
@@ -25370,23 +25371,23 @@
       </c>
       <c r="U153" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17</t>
+          <t>Q14, Q17, Q22, Q23</t>
         </is>
       </c>
       <c r="V153" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W153" s="6" t="inlineStr">
         <is>
-          <t>1. D4 is on screen
-2. the next question shown is Q22</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against D4</t>
         </is>
       </c>
       <c r="X153" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y153" s="6" t="inlineStr">
@@ -25416,7 +25417,7 @@
       </c>
       <c r="AD153" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE153" s="6" t="inlineStr">
@@ -25431,7 +25432,7 @@
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>Q22</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
@@ -25446,12 +25447,12 @@
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
@@ -25461,27 +25462,27 @@
       </c>
       <c r="H154" s="6" t="inlineStr">
         <is>
-          <t>D4 blocks a blank answer</t>
+          <t>Q22 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>Prove D4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q22 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L154" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as D4.</t>
+          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q22.</t>
         </is>
       </c>
       <c r="M154" s="6" t="inlineStr">
@@ -25491,33 +25492,33 @@
       </c>
       <c r="N154" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman
-then: At D4, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O154" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P154" s="6" t="inlineStr">
         <is>
-          <t>Every answer before D4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at D4 is the one the claim turns on.</t>
+          <t>Every answer before Q22 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q22 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q154" s="6" t="inlineStr">
         <is>
-          <t>At D4, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R154" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4  (refused at D4; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
       <c r="S154" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="T154" s="6" t="inlineStr">
@@ -25527,23 +25528,23 @@
       </c>
       <c r="U154" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17, Q22, Q23</t>
+          <t>Q14, Q17</t>
         </is>
       </c>
       <c r="V154" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W154" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against D4</t>
+          <t>1. Q22 is on screen
+2. the next question shown is Q23</t>
         </is>
       </c>
       <c r="X154" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y154" s="6" t="inlineStr">
@@ -25553,7 +25554,7 @@
       </c>
       <c r="Z154" s="6" t="inlineStr">
         <is>
-          <t>D4 | What is your household or organizational decision band? | single | Band 1; Band 2; Band 3; Band 4; Prefer not to say | Always show</t>
+          <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
         </is>
       </c>
       <c r="AA154" s="6" t="inlineStr">
@@ -25573,7 +25574,7 @@
       </c>
       <c r="AD154" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE154" s="6" t="inlineStr">
@@ -25603,12 +25604,12 @@
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
@@ -25618,22 +25619,22 @@
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>Q22 accepts a normal answer and the survey moves on</t>
+          <t>Q22 blocks a blank answer</t>
         </is>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q22 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q22 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr">
@@ -25648,13 +25649,13 @@
       </c>
       <c r="N155" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1
+then: At Q22, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O155" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P155" s="6" t="inlineStr">
@@ -25664,17 +25665,17 @@
       </c>
       <c r="Q155" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q22, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R155" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22  (refused at Q22; respondent stays put)</t>
         </is>
       </c>
       <c r="S155" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22</t>
         </is>
       </c>
       <c r="T155" s="6" t="inlineStr">
@@ -25684,23 +25685,23 @@
       </c>
       <c r="U155" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17</t>
+          <t>Q14, Q17, Q23</t>
         </is>
       </c>
       <c r="V155" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W155" s="6" t="inlineStr">
         <is>
-          <t>1. Q22 is on screen
-2. the next question shown is Q23</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q22</t>
         </is>
       </c>
       <c r="X155" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y155" s="6" t="inlineStr">
@@ -25730,7 +25731,7 @@
       </c>
       <c r="AD155" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE155" s="6" t="inlineStr">
@@ -25745,7 +25746,7 @@
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q23</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
@@ -25760,12 +25761,12 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
@@ -25775,27 +25776,27 @@
       </c>
       <c r="H156" s="6" t="inlineStr">
         <is>
-          <t>Q22 blocks a blank answer</t>
+          <t>Q23 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>Prove Q22 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q23 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K156" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L156" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q22.</t>
+          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
         </is>
       </c>
       <c r="M156" s="6" t="inlineStr">
@@ -25805,33 +25806,33 @@
       </c>
       <c r="N156" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1
-then: At Q22, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O156" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P156" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q22 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q22 is the one the claim turns on.</t>
+          <t>Every answer before Q23 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q23 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q156" s="6" t="inlineStr">
         <is>
-          <t>At Q22, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R156" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22  (refused at Q22; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
       <c r="S156" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22</t>
+          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
       <c r="T156" s="6" t="inlineStr">
@@ -25841,23 +25842,23 @@
       </c>
       <c r="U156" s="6" t="inlineStr">
         <is>
-          <t>Q14, Q17, Q23</t>
+          <t>Q14, Q17</t>
         </is>
       </c>
       <c r="V156" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W156" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q22</t>
+          <t>1. Q23 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X156" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y156" s="6" t="inlineStr">
@@ -25867,7 +25868,8 @@
       </c>
       <c r="Z156" s="6" t="inlineStr">
         <is>
-          <t>Q22 | May we use your anonymized comments in internal reporting? | single | Yes; No | Always show</t>
+          <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
+Optional</t>
         </is>
       </c>
       <c r="AA156" s="6" t="inlineStr">
@@ -25887,7 +25889,7 @@
       </c>
       <c r="AD156" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE156" s="6" t="inlineStr">
@@ -25917,7 +25919,7 @@
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
@@ -25932,17 +25934,17 @@
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>Q23 accepts a normal answer and the survey moves on</t>
+          <t>Q23 accepts a valid answer</t>
         </is>
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q23 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q23 accepts an answer that obeys its stated rule. The rule is: at most 1000 characters</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K157" s="6" t="inlineStr">
@@ -25963,12 +25965,12 @@
       <c r="N157" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q23, type “x”, then submit.</t>
         </is>
       </c>
       <c r="O157" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P157" s="6" t="inlineStr">
@@ -25978,7 +25980,7 @@
       </c>
       <c r="Q157" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q23, type “x”, then submit.</t>
         </is>
       </c>
       <c r="R157" s="6" t="inlineStr">
@@ -26008,8 +26010,7 @@
       </c>
       <c r="W157" s="6" t="inlineStr">
         <is>
-          <t>1. Q23 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X157" s="6" t="inlineStr">
@@ -26045,7 +26046,7 @@
       </c>
       <c r="AD157" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE157" s="6" t="inlineStr">
@@ -26080,7 +26081,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
@@ -26090,12 +26091,12 @@
       </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
-          <t>Q23 accepts a valid answer</t>
+          <t>Q23 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>Prove Q23 accepts an answer that obeys its stated rule. The rule is: at most 1000 characters</t>
+          <t>Prove Q23 refuses an answer that breaks its stated rule. The rule is: at most 1000 characters</t>
         </is>
       </c>
       <c r="J158" s="6" t="inlineStr">
@@ -26121,12 +26122,12 @@
       <c r="N158" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: At Q23, type “x”, then submit.</t>
+then: At Q23, type a 1001-character answer, then submit.</t>
         </is>
       </c>
       <c r="O158" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P158" s="6" t="inlineStr">
@@ -26136,12 +26137,12 @@
       </c>
       <c r="Q158" s="6" t="inlineStr">
         <is>
-          <t>At Q23, type “x”, then submit.</t>
+          <t>At Q23, type a 1001-character answer, then submit.</t>
         </is>
       </c>
       <c r="R158" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23  (refused at Q23; respondent stays put)</t>
         </is>
       </c>
       <c r="S158" s="6" t="inlineStr">
@@ -26161,17 +26162,18 @@
       </c>
       <c r="V158" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W158" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q23</t>
         </is>
       </c>
       <c r="X158" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y158" s="6" t="inlineStr">
@@ -26237,7 +26239,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
@@ -26247,22 +26249,22 @@
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
-          <t>Q23 rejects an invalid answer</t>
+          <t>Q23 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>Prove Q23 refuses an answer that breaks its stated rule. The rule is: at most 1000 characters</t>
+          <t>Prove Q23 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr">
@@ -26278,12 +26280,12 @@
       <c r="N159" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: At Q23, type a 1001-character answer, then submit.</t>
+then: At Q23, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O159" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P159" s="6" t="inlineStr">
@@ -26293,12 +26295,12 @@
       </c>
       <c r="Q159" s="6" t="inlineStr">
         <is>
-          <t>At Q23, type a 1001-character answer, then submit.</t>
+          <t>At Q23, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R159" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23  (refused at Q23; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
       <c r="S159" s="6" t="inlineStr">
@@ -26318,18 +26320,17 @@
       </c>
       <c r="V159" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W159" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q23</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X159" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y159" s="6" t="inlineStr">
@@ -26360,7 +26361,7 @@
       </c>
       <c r="AD159" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE159" s="6" t="inlineStr">
@@ -26405,22 +26406,22 @@
       </c>
       <c r="H160" s="6" t="inlineStr">
         <is>
-          <t>Q23 allows a blank answer, being optional</t>
+          <t>Q23 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>Prove Q23 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove Q23 refuses an answer that breaks its stated rule. The rule is: at most 1000 characters</t>
         </is>
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr">
@@ -26436,12 +26437,12 @@
       <c r="N160" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: At Q23, type nothing, then submit.</t>
+then: At Q23, type a 1000-character answer, then submit.</t>
         </is>
       </c>
       <c r="O160" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P160" s="6" t="inlineStr">
@@ -26451,7 +26452,7 @@
       </c>
       <c r="Q160" s="6" t="inlineStr">
         <is>
-          <t>At Q23, type nothing, then submit.</t>
+          <t>At Q23, type a 1000-character answer, then submit.</t>
         </is>
       </c>
       <c r="R160" s="6" t="inlineStr">
@@ -26517,7 +26518,7 @@
       </c>
       <c r="AD160" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE160" s="6" t="inlineStr">
@@ -26593,7 +26594,7 @@
       <c r="N161" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: At Q23, type a 1000-character answer, then submit.</t>
+then: At Q23, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O161" s="6" t="inlineStr">
@@ -26608,7 +26609,7 @@
       </c>
       <c r="Q161" s="6" t="inlineStr">
         <is>
-          <t>At Q23, type a 1000-character answer, then submit.</t>
+          <t>At Q23, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R161" s="6" t="inlineStr">
@@ -26719,22 +26720,22 @@
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>Q23 rejects an invalid answer</t>
+          <t>Q23 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>Prove Q23 refuses an answer that breaks its stated rule. The rule is: at most 1000 characters</t>
+          <t>Prove Q23 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr">
@@ -26750,7 +26751,7 @@
       <c r="N162" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: At Q23, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+then: At Q23, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O162" s="6" t="inlineStr">
@@ -26765,7 +26766,7 @@
       </c>
       <c r="Q162" s="6" t="inlineStr">
         <is>
-          <t>At Q23, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q23, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R162" s="6" t="inlineStr">
@@ -26831,12 +26832,12 @@
       </c>
       <c r="AD162" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE162" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: multi_equality</t>
+          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -26846,57 +26847,57 @@
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>whole survey</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>TC-FT150</t>
+          <t>TC-RT05</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
-          <t>Q23 allows a blank answer, being optional</t>
+          <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>Prove Q23 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr">
         <is>
-          <t>Travel path P11 (Completing respondent — Q1=None of these; Q10=No; Q12=Not resolved) as far as Q23.</t>
+          <t>Travel path P07 (Completing respondent — Q1=None of these) as far as the end.</t>
         </is>
       </c>
       <c r="M163" s="6" t="inlineStr">
@@ -26905,249 +26906,92 @@
         </is>
       </c>
       <c r="N163" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
-then: At Q23, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O163" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P163" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q23 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q23 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q163" s="6" t="inlineStr">
-        <is>
-          <t>At Q23, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R163" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
-        </is>
-      </c>
-      <c r="S163" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
-        </is>
-      </c>
-      <c r="T163" s="6" t="inlineStr">
-        <is>
-          <t>Q2, Q3</t>
-        </is>
-      </c>
-      <c r="U163" s="6" t="inlineStr">
-        <is>
-          <t>Q14, Q17</t>
-        </is>
-      </c>
-      <c r="V163" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W163" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X163" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y163" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z163" s="6" t="inlineStr">
-        <is>
-          <t>Q23 | Any final comments? | text | — | Validate: {"max_length": 1000}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA163" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB163" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC163" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD163" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE163" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: multi_equality, whitespace_is_an_answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="B164" s="9" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C164" s="7" t="inlineStr">
-        <is>
-          <t>TC-RT05</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>6. Termination / Disposition</t>
-        </is>
-      </c>
-      <c r="F164" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G164" s="7" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end journey: COMPLETE by way of routing</t>
-        </is>
-      </c>
-      <c r="I164" s="6" t="inlineStr">
-        <is>
-          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
-        </is>
-      </c>
-      <c r="J164" s="6" t="inlineStr">
-        <is>
-          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
-        </is>
-      </c>
-      <c r="K164" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="L164" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P07 (Completing respondent — Q1=None of these) as far as the end.</t>
-        </is>
-      </c>
-      <c r="M164" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N164" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Personally manage an ongoing chronic health condition; S3 = No; S4 = No; Q1 = Care Network A; Q2 = Care Network A; Q3 = Care Network A; Q4 = Recently diagnosed; Q5 = Primary-care physician; Q6 = Primary-care physician; Q7 = Very poor; Q8 = 0; Q9 = Q9-R1=Very poor; Q9-R2=Very poor; Q9-R3=Very poor; Q9-R4=Very poor; ...; Q10 = Yes; Q11 = Phone; Q12 = Fully; Q13 = Very low; Q15 = Yes; Q16 = Price; Q18 = Price=20; Quality=20; Convenience=20; Trust=20; ...; Q19 = Concept A; Q20 = Very poor; Q21 = xxxxx; D1 = North; D2 = 21-29; D3 = Woman; D4 = Band 1; Q22 = Yes
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O164" s="6" t="inlineStr">
+      <c r="O163" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P164" s="6" t="inlineStr">
+      <c r="P163" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q164" s="6" t="inlineStr">
+      <c r="Q163" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R164" s="6" t="inlineStr">
+      <c r="R163" s="6" t="inlineStr">
         <is>
           <t>S1 -&gt; S2 -&gt; S3 -&gt; S4 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8 -&gt; Q9 -&gt; DT2 -&gt; Q10 -&gt; Q11 -&gt; Q12 -&gt; Q13 -&gt; Q15 -&gt; Q16 -&gt; Q18 -&gt; Q19 -&gt; Q20 -&gt; Q21 -&gt; DT3 -&gt; D1 -&gt; D2 -&gt; D3 -&gt; D4 -&gt; Q22 -&gt; Q23</t>
         </is>
       </c>
-      <c r="S164" s="6" t="inlineStr">
+      <c r="S163" s="6" t="inlineStr">
         <is>
           <t>S1, S2, S3, S4, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, DT2, Q10, Q11, Q12, Q13, Q15, Q16, Q18, Q19, Q20, Q21, DT3, D1, D2, D3, D4, Q22, Q23</t>
         </is>
       </c>
-      <c r="T164" s="6" t="inlineStr">
+      <c r="T163" s="6" t="inlineStr">
         <is>
           <t>Q2, Q3</t>
         </is>
       </c>
-      <c r="U164" s="6" t="inlineStr">
+      <c r="U163" s="6" t="inlineStr">
         <is>
           <t>Q14, Q17</t>
         </is>
       </c>
-      <c r="V164" s="6" t="inlineStr">
+      <c r="V163" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W164" s="6" t="inlineStr">
+      <c r="W163" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X164" s="6" t="inlineStr">
+      <c r="X163" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y164" s="6" t="inlineStr">
+      <c r="Y163" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z164" s="6" t="inlineStr">
+      <c r="Z163" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA164" s="6" t="inlineStr">
+      <c r="AA163" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB164" s="10" t="inlineStr">
+      <c r="AB163" s="10" t="inlineStr">
         <is>
           <t>PROVISIONAL</t>
         </is>
       </c>
-      <c r="AC164" s="8" t="inlineStr">
+      <c r="AC163" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD164" s="6" t="inlineStr">
+      <c r="AD163" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE164" s="6" t="inlineStr">
+      <c r="AE163" s="6" t="inlineStr">
         <is>
           <t>Leans on an unconfirmed reading: multi_equality</t>
         </is>
